--- a/forms/trg/Formulir_TRG_glohamod.xlsx
+++ b/forms/trg/Formulir_TRG_glohamod.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B31)</f>
+        <f>COUNTA(Anggota!B5:B32)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F31)</f>
+        <f>COUNTA(Anggota!F5:F32)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,12 +913,12 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Dr. Samsu Arif, M.Si.</t>
+          <t>Prof. Dr. Eng. Amiruddin, S.Si., M.Si.</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="12" t="n"/>
@@ -931,7 +931,7 @@
       <c r="K5" s="12" t="n"/>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>56237390100</t>
+          <t>57194349826</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Dr. Eng. Muh. Alimuddin Hamzah, M.Eng.</t>
+          <t>Dr. Samsu Arif, M.Si.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="12" t="n"/>
@@ -964,7 +964,7 @@
       <c r="K6" s="12" t="n"/>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>57194349826</t>
+          <t>56237390100</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Sakka, M.Si.</t>
+          <t>Dr. Eng. Muh. Alimuddin Hamzah, M.Eng.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="12" t="n"/>
@@ -997,7 +997,7 @@
       <c r="K7" s="12" t="n"/>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>57210919780</t>
+          <t>57194349826</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Dr. Muh. Altin Massinai, M.T.Surv.</t>
+          <t>Dr. Sakka, M.Si.</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
@@ -1030,7 +1030,7 @@
       <c r="K8" s="12" t="n"/>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>56943550600</t>
+          <t>57210919780</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1045,19 +1045,15 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Prof. Sangyoung Son</t>
+          <t>Dr. Muh. Altin Massinai, M.T.Surv.</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>Coastal Hydrodynamics Laboratory, School of Civil, Environmental, and Architectural Engineering, Korea University</t>
-        </is>
-      </c>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n"/>
       <c r="E9" s="11" t="n"/>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
@@ -1067,7 +1063,7 @@
       <c r="K9" s="12" t="n"/>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>55835324700</t>
+          <t>56943550600</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1082,17 +1078,17 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Dr. Lujia Feng</t>
+          <t>Prof. Sangyoung Son</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Asean School of Environment, College of Science, Nanyang Technological University, Singapore</t>
+          <t>Coastal Hydrodynamics Laboratory, School of Civil, Environmental, and Architectural Engineering, Korea University</t>
         </is>
       </c>
       <c r="E10" s="11" t="n"/>
@@ -1104,7 +1100,7 @@
       <c r="K10" s="12" t="n"/>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>34979853900</t>
+          <t>55835324700</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -1119,15 +1115,19 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Drs. Erfan Syamsuddin, M.Si.</t>
+          <t>Dr. Lujia Feng</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="n"/>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Asean School of Environment, College of Science, Nanyang Technological University, Singapore</t>
+        </is>
+      </c>
       <c r="E11" s="11" t="n"/>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
@@ -1137,7 +1137,7 @@
       <c r="K11" s="12" t="n"/>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>57211095110</t>
+          <t>34979853900</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Syamsuddin, S.Si., M.T.</t>
+          <t>Drs. Erfan Syamsuddin, M.Si.</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D12" s="12" t="n"/>
@@ -1170,7 +1170,7 @@
       <c r="K12" s="12" t="n"/>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>57201665528</t>
+          <t>57211095110</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Saaduddin, M.Sc.</t>
+          <t>Syamsuddin, S.Si., M.T.</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="12" t="n"/>
@@ -1203,7 +1203,7 @@
       <c r="K13" s="12" t="n"/>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>57201350829</t>
+          <t>57201665528</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Andi Muhamad Pramatadie, S.T., M.Eng., Ph.D.</t>
+          <t>Saaduddin, M.Sc.</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D14" s="12" t="n"/>
@@ -1236,7 +1236,7 @@
       <c r="K14" s="12" t="n"/>
       <c r="L14" s="11" t="inlineStr">
         <is>
-          <t>55850581900</t>
+          <t>57201350829</t>
         </is>
       </c>
       <c r="M14" s="11" t="inlineStr">
@@ -1251,12 +1251,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Dr. Muhammad Taufiq Rafie, M.T.</t>
+          <t>Andi Muhamad Pramatadie, S.T., M.Eng., Ph.D.</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
@@ -1269,7 +1269,7 @@
       <c r="K15" s="12" t="n"/>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>57204974123</t>
+          <t>55850581900</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Aswar Syafnur, S.Si., M.Eng.</t>
+          <t>Dr. Muhammad Taufiq Rafie, M.T.</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D16" s="12" t="n"/>
@@ -1302,7 +1302,7 @@
       <c r="K16" s="12" t="n"/>
       <c r="L16" s="11" t="inlineStr">
         <is>
-          <t>58203829200</t>
+          <t>57204974123</t>
         </is>
       </c>
       <c r="M16" s="11" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Sri Wahyunia</t>
+          <t>Aswar Syafnur, S.Si., M.Eng.</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D17" s="12" t="n"/>
@@ -1333,7 +1333,11 @@
       <c r="I17" s="12" t="n"/>
       <c r="J17" s="12" t="n"/>
       <c r="K17" s="12" t="n"/>
-      <c r="L17" s="12" t="n"/>
+      <c r="L17" s="11" t="inlineStr">
+        <is>
+          <t>58203829200</t>
+        </is>
+      </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1346,12 +1350,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Muh. Faqih Raihan</t>
+          <t>Sri Wahyunia</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D18" s="12" t="n"/>
@@ -1375,15 +1379,19 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Muh. Farid Wajedy, S.Si., M.Si.</t>
+          <t>Muh. Faqih Raihan</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="n"/>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>The Global Hazard Modeling Research Group (GLOHAMOD) is an interdisciplinary research initiative established under Universitas Hasanuddin’s strategic policy to develop Thematic Research Groups. This research cluster integrates expertise from geosciences, natural sciences, and social humanities to address both natural and non-natural disasters through scientific, technological, and socio-humanistic approaches.</t>
+        </is>
+      </c>
       <c r="E19" s="11" t="n"/>
       <c r="F19" s="12" t="n"/>
       <c r="G19" s="12" t="n"/>
@@ -1391,11 +1399,7 @@
       <c r="I19" s="12" t="n"/>
       <c r="J19" s="12" t="n"/>
       <c r="K19" s="12" t="n"/>
-      <c r="L19" s="11" t="inlineStr">
-        <is>
-          <t>59217049300</t>
-        </is>
-      </c>
+      <c r="L19" s="12" t="n"/>
       <c r="M19" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1406,8 +1410,16 @@
       <c r="A20" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="12" t="n"/>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Muh. Farid Wajedy, S.Si., M.Si.</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Researcher</t>
+        </is>
+      </c>
       <c r="D20" s="12" t="n"/>
       <c r="E20" s="11" t="n"/>
       <c r="F20" s="12" t="n"/>
@@ -1416,8 +1428,16 @@
       <c r="I20" s="12" t="n"/>
       <c r="J20" s="12" t="n"/>
       <c r="K20" s="12" t="n"/>
-      <c r="L20" s="12" t="n"/>
-      <c r="M20" s="12" t="n"/>
+      <c r="L20" s="11" t="inlineStr">
+        <is>
+          <t>59217049300</t>
+        </is>
+      </c>
+      <c r="M20" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1606,15 +1626,32 @@
       <c r="L31" s="12" t="n"/>
       <c r="M31" s="12" t="n"/>
     </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="11" t="n"/>
+      <c r="F32" s="12" t="n"/>
+      <c r="G32" s="12" t="n"/>
+      <c r="H32" s="12" t="n"/>
+      <c r="I32" s="12" t="n"/>
+      <c r="J32" s="12" t="n"/>
+      <c r="K32" s="12" t="n"/>
+      <c r="L32" s="12" t="n"/>
+      <c r="M32" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
